--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0001T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.79153595451278</v>
+        <v>7.116124592608327</v>
       </c>
       <c r="D2" t="n">
-        <v>43.84534904668121</v>
+        <v>7.124869220085698</v>
       </c>
       <c r="E2" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F2" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>65.17687193752204</v>
+        <v>10.59124168984733</v>
       </c>
       <c r="D3" t="n">
-        <v>65.10505907748035</v>
+        <v>10.57957210009056</v>
       </c>
       <c r="E3" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F3" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>82.74183248128159</v>
+        <v>13.44554777820826</v>
       </c>
       <c r="D4" t="n">
-        <v>82.08293002238557</v>
+        <v>13.33847612863766</v>
       </c>
       <c r="E4" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F4" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.53641148236354</v>
+        <v>2.524666865884076</v>
       </c>
       <c r="D5" t="n">
-        <v>15.69903086545104</v>
+        <v>2.551092515635795</v>
       </c>
       <c r="E5" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F5" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.58237439695365</v>
+        <v>1.394635839504968</v>
       </c>
       <c r="D6" t="n">
-        <v>10.43857146374985</v>
+        <v>1.696267862859351</v>
       </c>
       <c r="E6" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F6" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>17.20582029841463</v>
+        <v>2.795945798492377</v>
       </c>
       <c r="D7" t="n">
-        <v>13.21883078072896</v>
+        <v>2.148060001868456</v>
       </c>
       <c r="E7" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F7" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.95143317178233</v>
+        <v>3.892107890414629</v>
       </c>
       <c r="D8" t="n">
-        <v>5.718517131806441</v>
+        <v>0.9292590339185467</v>
       </c>
       <c r="E8" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F8" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>55.69477592902828</v>
+        <v>9.050401088467096</v>
       </c>
       <c r="D9" t="n">
-        <v>55.04435666020071</v>
+        <v>8.944707957282615</v>
       </c>
       <c r="E9" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F9" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.66449153719896</v>
+        <v>2.707979874794831</v>
       </c>
       <c r="D10" t="n">
-        <v>15.84046171424641</v>
+        <v>2.574075028565041</v>
       </c>
       <c r="E10" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F10" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.02684167591831</v>
+        <v>4.066861772336725</v>
       </c>
       <c r="D11" t="n">
-        <v>24.23237658382163</v>
+        <v>3.937761194871015</v>
       </c>
       <c r="E11" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F11" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.67368024147667</v>
+        <v>4.659473039239959</v>
       </c>
       <c r="D12" t="n">
-        <v>27.85759925274022</v>
+        <v>4.526859878570286</v>
       </c>
       <c r="E12" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F12" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>30.1081384346492</v>
+        <v>4.892572495630494</v>
       </c>
       <c r="D13" t="n">
-        <v>42.02407434295325</v>
+        <v>6.828912080729904</v>
       </c>
       <c r="E13" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F13" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.92505818240037</v>
+        <v>4.37532195464006</v>
       </c>
       <c r="D14" t="n">
-        <v>27.48376400784999</v>
+        <v>4.466111651275623</v>
       </c>
       <c r="E14" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F14" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>10.83589777840467</v>
+        <v>1.760833388990758</v>
       </c>
       <c r="D15" t="n">
-        <v>40.2125388058827</v>
+        <v>6.534537555955939</v>
       </c>
       <c r="E15" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F15" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>55.77828476919678</v>
+        <v>9.063971274994477</v>
       </c>
       <c r="D16" t="n">
-        <v>56.36718575823443</v>
+        <v>9.159667685713094</v>
       </c>
       <c r="E16" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F16" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>67.28208711902047</v>
+        <v>10.93333915684083</v>
       </c>
       <c r="D17" t="n">
-        <v>65.14627674572709</v>
+        <v>10.58626997118065</v>
       </c>
       <c r="E17" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F17" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>20.98809186181536</v>
+        <v>3.410564927544995</v>
       </c>
       <c r="D18" t="n">
-        <v>47.84842162825114</v>
+        <v>7.77536851459081</v>
       </c>
       <c r="E18" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F18" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>33.24154027718932</v>
+        <v>5.401750295043265</v>
       </c>
       <c r="D19" t="n">
-        <v>41.94138597284757</v>
+        <v>6.81547522058773</v>
       </c>
       <c r="E19" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F19" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>78.92614851961014</v>
+        <v>12.82549913443665</v>
       </c>
       <c r="D20" t="n">
-        <v>79.55739381172971</v>
+        <v>12.92807649440608</v>
       </c>
       <c r="E20" t="n">
-        <v>22.79082431661007</v>
+        <v>3.703508951449135</v>
       </c>
       <c r="F20" t="n">
-        <v>22.56001135911463</v>
+        <v>3.666001845856127</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
